--- a/filesystem/MarketingOps/CRM/closed_won_revenue_export.xlsx
+++ b/filesystem/MarketingOps/CRM/closed_won_revenue_export.xlsx
@@ -241,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -374,11 +374,53 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000EA5E9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -566,6 +608,8 @@
     <xf numFmtId="164" fontId="26" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -886,7 +930,6 @@
           <t>Closed-Won Revenue Export — Trailing 12 Months</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
@@ -894,7 +937,6 @@
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
     </row>
     <row r="3" ht="14" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
@@ -976,7 +1018,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n"/>
+      <c r="B11" s="69" t="n"/>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
@@ -1055,7 +1097,7 @@
           <t>Methodology Note</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n"/>
+      <c r="B20" s="69" t="n"/>
     </row>
     <row r="21" ht="72" customHeight="1">
       <c r="A21" s="42" t="inlineStr">
@@ -1063,7 +1105,7 @@
           <t>The Average Revenue per SQL figure above is computed across the Sales-Touched subset only, consistent with the SQL Definitions &amp; Pipeline Reporting Standards memo v1.2 (Grace Feldman, 10/15/2025). Self-Serve Trial closed-wons are tracked separately by Product Marketing and are excluded from the trailing 12-month per-SQL average feeding pipeline forecasts. See the SQL Definitions &amp; Pipeline Reporting Standards memo v1.2 for the applicable lead-count definition.</t>
         </is>
       </c>
-      <c r="B21" s="42" t="n"/>
+      <c r="B21" s="70" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1"/>
     <row r="23" ht="20" customHeight="1">
@@ -1167,7 +1209,7 @@
       </c>
       <c r="B2" s="50" t="inlineStr">
         <is>
-          <t>Meridian Biosystems</t>
+          <t>Thistlewood Biosystems</t>
         </is>
       </c>
       <c r="C2" s="51" t="n">
@@ -1683,7 +1725,7 @@
       </c>
       <c r="G17" s="62" t="inlineStr">
         <is>
-          <t>Referred by Meridian Biosystems</t>
+          <t>Referred by Thistlewood Biosystems</t>
         </is>
       </c>
     </row>

--- a/filesystem/MarketingOps/CRM/closed_won_revenue_export.xlsx
+++ b/filesystem/MarketingOps/CRM/closed_won_revenue_export.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -175,6 +175,16 @@
       <color rgb="000F172A"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF334155"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -241,7 +251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -416,11 +426,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="000EA5E9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -610,6 +626,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -932,7 +957,7 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="73" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
@@ -1013,7 +1038,7 @@
     </row>
     <row r="10" ht="16" customHeight="1"/>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
@@ -1092,7 +1117,7 @@
     </row>
     <row r="19" ht="16" customHeight="1"/>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>Methodology Note</t>
         </is>
@@ -1121,14 +1146,14 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
         <is>
           <t>Director, Analytics &amp; Reporting</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="72" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
